--- a/! Hex Colors.xlsx
+++ b/! Hex Colors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\My Drive\kent state ashtabula\11 Fall 2025\IT 11006 - Intro to Web Site Technology\Portfolio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Beau\Portfolio-Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BAF800A-53A9-49CC-BDB0-06FB0C908A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C101365-95CF-422C-8A42-AFB88EA6548B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26100" yWindow="5220" windowWidth="21600" windowHeight="10260" xr2:uid="{173DCCF7-EA23-44A1-AC6B-75A9D60C3906}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{173DCCF7-EA23-44A1-AC6B-75A9D60C3906}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>#faf2fd</t>
   </si>
@@ -57,6 +57,9 @@
   </si>
   <si>
     <t>#FF0000</t>
+  </si>
+  <si>
+    <t>#fcf8fe</t>
   </si>
 </sst>
 </file>
@@ -78,7 +81,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -118,6 +121,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF8FE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -134,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -143,6 +152,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -151,6 +161,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFCF8FE"/>
       <color rgb="FF000000"/>
       <color rgb="FF877090"/>
       <color rgb="FFEEE3F1"/>
@@ -486,49 +497,53 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82DD1428-8413-4A10-8D4B-91CB74889C11}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B1" s="2"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="7"/>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B1" s="8"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="7"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
     </row>
